--- a/Kameraman_metadata.xlsx
+++ b/Kameraman_metadata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/selimcalli/Documents/onemli belgeler/04-PROJELER/EU PROJECT/02_DATA/Mediterranean/00_ALL_SPRING_LIST/02_discharge_edited/01_Metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE09EBA-DD97-E74F-A2B2-DB99DD86D6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94192007-332C-1E4F-B474-EAE7E2AFF2ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7785,10 +7785,10 @@
         <v>19</v>
       </c>
       <c r="F114" s="80">
-        <v>42.843000000000004</v>
+        <v>43.015999999999998</v>
       </c>
       <c r="G114" s="80">
-        <v>2.2029999999999998</v>
+        <v>0.73799999999999999</v>
       </c>
       <c r="H114" s="81">
         <v>317</v>
@@ -7831,10 +7831,10 @@
         <v>19</v>
       </c>
       <c r="F115" s="80">
-        <v>42.984000000000002</v>
+        <v>42.984999999999999</v>
       </c>
       <c r="G115" s="80">
-        <v>0.9</v>
+        <v>0.90200000000000002</v>
       </c>
       <c r="H115" s="81">
         <v>435</v>
@@ -7875,10 +7875,10 @@
         <v>19</v>
       </c>
       <c r="F116" s="80">
-        <v>43.031999999999996</v>
+        <v>43.024999999999999</v>
       </c>
       <c r="G116" s="80">
-        <v>0.51300000000000001</v>
+        <v>0.52700000000000002</v>
       </c>
       <c r="H116" s="81">
         <v>525</v>
@@ -8566,10 +8566,10 @@
         <v>360</v>
       </c>
     </row>
-    <row r="131" spans="1:16" ht="14">
+    <row r="131" spans="1:16" ht="15">
       <c r="D131" s="99"/>
     </row>
-    <row r="132" spans="1:16" ht="14">
+    <row r="132" spans="1:16" ht="15">
       <c r="D132" s="100"/>
       <c r="E132" s="101"/>
       <c r="F132" s="100"/>
